--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330348</v>
+        <v>122330548</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>100441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651275</v>
+        <v>651297</v>
       </c>
       <c r="R3" t="n">
-        <v>6674023</v>
+        <v>6673956</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -883,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330548</v>
+        <v>122330349</v>
       </c>
       <c r="B4" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,31 +924,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651297</v>
+        <v>651319</v>
       </c>
       <c r="R4" t="n">
-        <v>6673956</v>
+        <v>6673998</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330349</v>
+        <v>122330399</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>90779</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,35 +1052,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651319</v>
+        <v>651326</v>
       </c>
       <c r="R5" t="n">
-        <v>6673998</v>
+        <v>6673994</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1123,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1133,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330399</v>
+        <v>122330348</v>
       </c>
       <c r="B6" t="n">
-        <v>90779</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,26 +1167,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651326</v>
+        <v>651275</v>
       </c>
       <c r="R6" t="n">
-        <v>6673994</v>
+        <v>6674023</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330330</v>
+        <v>122330399</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>90789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651327</v>
+        <v>651326</v>
       </c>
       <c r="R2" t="n">
-        <v>6673995</v>
+        <v>6673994</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -796,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330548</v>
+        <v>122330348</v>
       </c>
       <c r="B3" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651297</v>
+        <v>651275</v>
       </c>
       <c r="R3" t="n">
-        <v>6673956</v>
+        <v>6674023</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -875,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1036,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330399</v>
+        <v>122330548</v>
       </c>
       <c r="B5" t="n">
-        <v>90779</v>
+        <v>100451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,30 +1050,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651326</v>
+        <v>651297</v>
       </c>
       <c r="R5" t="n">
-        <v>6673994</v>
+        <v>6673956</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330348</v>
+        <v>122330330</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,37 +1166,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651275</v>
+        <v>651327</v>
       </c>
       <c r="R6" t="n">
-        <v>6674023</v>
+        <v>6673995</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330399</v>
+        <v>122330548</v>
       </c>
       <c r="B2" t="n">
-        <v>90789</v>
+        <v>100451</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651326</v>
+        <v>651297</v>
       </c>
       <c r="R2" t="n">
-        <v>6673994</v>
+        <v>6673956</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330348</v>
+        <v>122330330</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651275</v>
+        <v>651327</v>
       </c>
       <c r="R3" t="n">
-        <v>6674023</v>
+        <v>6673995</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1038,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330548</v>
+        <v>122330399</v>
       </c>
       <c r="B5" t="n">
-        <v>100451</v>
+        <v>90789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,31 +1048,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1082,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651297</v>
+        <v>651326</v>
       </c>
       <c r="R5" t="n">
-        <v>6673956</v>
+        <v>6673994</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1117,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330330</v>
+        <v>122330348</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,34 +1163,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651327</v>
+        <v>651275</v>
       </c>
       <c r="R6" t="n">
-        <v>6673995</v>
+        <v>6674023</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330548</v>
+        <v>122330399</v>
       </c>
       <c r="B2" t="n">
-        <v>100451</v>
+        <v>90801</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651297</v>
+        <v>651326</v>
       </c>
       <c r="R2" t="n">
-        <v>6673956</v>
+        <v>6673994</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330330</v>
+        <v>122330548</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>100463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,32 +806,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651327</v>
+        <v>651297</v>
       </c>
       <c r="R3" t="n">
-        <v>6673995</v>
+        <v>6673956</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -875,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +909,7 @@
         <v>122330349</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1036,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330399</v>
+        <v>122330330</v>
       </c>
       <c r="B5" t="n">
-        <v>90789</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,30 +1042,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651326</v>
+        <v>651327</v>
       </c>
       <c r="R5" t="n">
-        <v>6673994</v>
+        <v>6673995</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1154,7 +1154,7 @@
         <v>122330348</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330399</v>
+        <v>122330330</v>
       </c>
       <c r="B2" t="n">
-        <v>90801</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651326</v>
+        <v>651327</v>
       </c>
       <c r="R2" t="n">
-        <v>6673994</v>
+        <v>6673995</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -790,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330548</v>
+        <v>122330348</v>
       </c>
       <c r="B3" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +808,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651297</v>
+        <v>651275</v>
       </c>
       <c r="R3" t="n">
-        <v>6673956</v>
+        <v>6674023</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -869,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1030,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330330</v>
+        <v>122330399</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>90808</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,36 +1056,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651327</v>
+        <v>651326</v>
       </c>
       <c r="R5" t="n">
-        <v>6673995</v>
+        <v>6673994</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1151,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330348</v>
+        <v>122330548</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1171,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651275</v>
+        <v>651297</v>
       </c>
       <c r="R6" t="n">
-        <v>6674023</v>
+        <v>6673956</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330348</v>
+        <v>122330349</v>
       </c>
       <c r="B3" t="n">
         <v>57395</v>
@@ -838,7 +838,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651275</v>
+        <v>651319</v>
       </c>
       <c r="R3" t="n">
-        <v>6674023</v>
+        <v>6673998</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330349</v>
+        <v>122330348</v>
       </c>
       <c r="B4" t="n">
         <v>57395</v>
@@ -962,7 +962,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651319</v>
+        <v>651275</v>
       </c>
       <c r="R4" t="n">
-        <v>6673998</v>
+        <v>6674023</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330330</v>
+        <v>122330348</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -724,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651327</v>
+        <v>651275</v>
       </c>
       <c r="R2" t="n">
-        <v>6673995</v>
+        <v>6674023</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -814,11 +812,6 @@
       <c r="E3" t="n">
         <v>100049</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -920,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330348</v>
+        <v>122330330</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,37 +925,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -972,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651275</v>
+        <v>651327</v>
       </c>
       <c r="R4" t="n">
-        <v>6674023</v>
+        <v>6673995</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1007,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,7 +1032,7 @@
         <v>122330399</v>
       </c>
       <c r="B5" t="n">
-        <v>90808</v>
+        <v>90813</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,11 +1046,6 @@
       </c>
       <c r="E5" t="n">
         <v>1202</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1162,7 +1142,7 @@
         <v>122330548</v>
       </c>
       <c r="B6" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,11 +1156,6 @@
       </c>
       <c r="E6" t="n">
         <v>222498</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330348</v>
+        <v>122330330</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651275</v>
+        <v>651327</v>
       </c>
       <c r="R2" t="n">
-        <v>6674023</v>
+        <v>6673995</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +799,7 @@
         <v>122330349</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,6 +813,11 @@
       </c>
       <c r="E3" t="n">
         <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -913,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330330</v>
+        <v>122330348</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,29 +932,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -957,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651327</v>
+        <v>651275</v>
       </c>
       <c r="R4" t="n">
-        <v>6673995</v>
+        <v>6674023</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -992,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330399</v>
+        <v>122330548</v>
       </c>
       <c r="B5" t="n">
-        <v>90813</v>
+        <v>100490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1056,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651326</v>
+        <v>651297</v>
       </c>
       <c r="R5" t="n">
-        <v>6673994</v>
+        <v>6673956</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1133,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330548</v>
+        <v>122330399</v>
       </c>
       <c r="B6" t="n">
-        <v>100477</v>
+        <v>90826</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,26 +1172,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651297</v>
+        <v>651326</v>
       </c>
       <c r="R6" t="n">
-        <v>6673956</v>
+        <v>6673994</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1213,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330330</v>
+        <v>122330348</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -724,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651327</v>
+        <v>651275</v>
       </c>
       <c r="R2" t="n">
-        <v>6673995</v>
+        <v>6674023</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330349</v>
+        <v>122330330</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +811,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651319</v>
+        <v>651327</v>
       </c>
       <c r="R3" t="n">
-        <v>6673998</v>
+        <v>6673995</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330348</v>
+        <v>122330399</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>90839</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,35 +936,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651275</v>
+        <v>651326</v>
       </c>
       <c r="R4" t="n">
-        <v>6674023</v>
+        <v>6673994</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1007,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,7 +1038,7 @@
         <v>122330548</v>
       </c>
       <c r="B5" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1160,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330399</v>
+        <v>122330349</v>
       </c>
       <c r="B6" t="n">
-        <v>90826</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,26 +1167,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651326</v>
+        <v>651319</v>
       </c>
       <c r="R6" t="n">
-        <v>6673994</v>
+        <v>6673998</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330348</v>
+        <v>122330548</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651275</v>
+        <v>651297</v>
       </c>
       <c r="R2" t="n">
-        <v>6674023</v>
+        <v>6673956</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330330</v>
+        <v>122330348</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,34 +803,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651327</v>
+        <v>651275</v>
       </c>
       <c r="R3" t="n">
-        <v>6673995</v>
+        <v>6674023</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -883,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1035,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330548</v>
+        <v>122330330</v>
       </c>
       <c r="B5" t="n">
-        <v>100503</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,27 +1046,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651297</v>
+        <v>651327</v>
       </c>
       <c r="R5" t="n">
-        <v>6673956</v>
+        <v>6673995</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330548</v>
+        <v>122330348</v>
       </c>
       <c r="B2" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651297</v>
+        <v>651275</v>
       </c>
       <c r="R2" t="n">
-        <v>6673956</v>
+        <v>6674023</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330348</v>
+        <v>122330330</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +811,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -843,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651275</v>
+        <v>651327</v>
       </c>
       <c r="R3" t="n">
-        <v>6674023</v>
+        <v>6673995</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +923,7 @@
         <v>122330399</v>
       </c>
       <c r="B4" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1030,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330330</v>
+        <v>122330548</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>100506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,32 +1051,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651327</v>
+        <v>651297</v>
       </c>
       <c r="R5" t="n">
-        <v>6673995</v>
+        <v>6673956</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330348</v>
+        <v>122330399</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>90833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651275</v>
+        <v>651326</v>
       </c>
       <c r="R2" t="n">
-        <v>6674023</v>
+        <v>6673994</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330330</v>
+        <v>122330348</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,34 +802,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651327</v>
+        <v>651275</v>
       </c>
       <c r="R3" t="n">
-        <v>6673995</v>
+        <v>6674023</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -883,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330399</v>
+        <v>122330330</v>
       </c>
       <c r="B4" t="n">
-        <v>90833</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,30 +926,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651326</v>
+        <v>651327</v>
       </c>
       <c r="R4" t="n">
-        <v>6673994</v>
+        <v>6673995</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330548</v>
+        <v>122330349</v>
       </c>
       <c r="B5" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,31 +1047,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651297</v>
+        <v>651319</v>
       </c>
       <c r="R5" t="n">
-        <v>6673956</v>
+        <v>6673998</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330349</v>
+        <v>122330548</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1171,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651319</v>
+        <v>651297</v>
       </c>
       <c r="R6" t="n">
-        <v>6673998</v>
+        <v>6673956</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330399</v>
+        <v>122330349</v>
       </c>
       <c r="B2" t="n">
-        <v>90833</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651326</v>
+        <v>651319</v>
       </c>
       <c r="R2" t="n">
-        <v>6673994</v>
+        <v>6673998</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330348</v>
+        <v>122330330</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +811,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651275</v>
+        <v>651327</v>
       </c>
       <c r="R3" t="n">
-        <v>6674023</v>
+        <v>6673995</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330330</v>
+        <v>122330399</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>90834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,36 +932,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651327</v>
+        <v>651326</v>
       </c>
       <c r="R4" t="n">
-        <v>6673995</v>
+        <v>6673994</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330349</v>
+        <v>122330348</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651319</v>
+        <v>651275</v>
       </c>
       <c r="R5" t="n">
-        <v>6673998</v>
+        <v>6674023</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,7 +1162,7 @@
         <v>122330548</v>
       </c>
       <c r="B6" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330399</v>
+        <v>122330348</v>
       </c>
       <c r="B4" t="n">
-        <v>90834</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,26 +936,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651326</v>
+        <v>651275</v>
       </c>
       <c r="R4" t="n">
-        <v>6673994</v>
+        <v>6674023</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -998,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330348</v>
+        <v>122330399</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>90834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,35 +1060,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651275</v>
+        <v>651326</v>
       </c>
       <c r="R5" t="n">
-        <v>6674023</v>
+        <v>6673994</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330349</v>
+        <v>122330330</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651319</v>
+        <v>651327</v>
       </c>
       <c r="R2" t="n">
-        <v>6673998</v>
+        <v>6673995</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330330</v>
+        <v>122330349</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,34 +808,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651327</v>
+        <v>651319</v>
       </c>
       <c r="R3" t="n">
-        <v>6673995</v>
+        <v>6673998</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330348</v>
+        <v>122330399</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>90837</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,35 +936,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651275</v>
+        <v>651326</v>
       </c>
       <c r="R4" t="n">
-        <v>6674023</v>
+        <v>6673994</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1007,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330399</v>
+        <v>122330348</v>
       </c>
       <c r="B5" t="n">
-        <v>90834</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,26 +1051,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651326</v>
+        <v>651275</v>
       </c>
       <c r="R5" t="n">
-        <v>6673994</v>
+        <v>6674023</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,7 +1162,7 @@
         <v>122330548</v>
       </c>
       <c r="B6" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330330</v>
+        <v>122330399</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>90837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651327</v>
+        <v>651326</v>
       </c>
       <c r="R2" t="n">
-        <v>6673995</v>
+        <v>6673994</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -920,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330399</v>
+        <v>122330348</v>
       </c>
       <c r="B4" t="n">
-        <v>90837</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,26 +930,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651326</v>
+        <v>651275</v>
       </c>
       <c r="R4" t="n">
-        <v>6673994</v>
+        <v>6674023</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -998,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330348</v>
+        <v>122330548</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,39 +1050,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651275</v>
+        <v>651297</v>
       </c>
       <c r="R5" t="n">
-        <v>6674023</v>
+        <v>6673956</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1122,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330548</v>
+        <v>122330330</v>
       </c>
       <c r="B6" t="n">
-        <v>100510</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,27 +1170,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651297</v>
+        <v>651327</v>
       </c>
       <c r="R6" t="n">
-        <v>6673956</v>
+        <v>6673995</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330399</v>
+        <v>129173806</v>
       </c>
       <c r="B2" t="n">
-        <v>90837</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651326</v>
+        <v>651274</v>
       </c>
       <c r="R2" t="n">
-        <v>6673994</v>
+        <v>6673866</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -748,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,62 +785,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330349</v>
+        <v>129173762</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Ackarebottnen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651319</v>
+        <v>651271</v>
       </c>
       <c r="R3" t="n">
-        <v>6673998</v>
+        <v>6673857</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -872,22 +853,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330348</v>
+        <v>129173810</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,35 +906,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651275</v>
+        <v>651294</v>
       </c>
       <c r="R4" t="n">
-        <v>6674023</v>
+        <v>6673877</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -996,22 +971,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,54 +1013,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330548</v>
+        <v>129173809</v>
       </c>
       <c r="B5" t="n">
-        <v>100510</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Ackarebottnen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651297</v>
+        <v>651237</v>
       </c>
       <c r="R5" t="n">
-        <v>6673956</v>
+        <v>6673840</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1112,22 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330330</v>
+        <v>122330399</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>90837</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,36 +1135,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651327</v>
+        <v>651326</v>
       </c>
       <c r="R6" t="n">
-        <v>6673995</v>
+        <v>6673994</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1272,6 +1235,1516 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122330349</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57400</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>651319</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6673998</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122330348</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57400</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>651275</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6674023</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122330548</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100510</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>651297</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6673956</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122330330</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>651327</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6673995</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129173815</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92854</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>651373</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6673998</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129173816</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92854</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>651311</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6673958</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129173744</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>651279</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6673952</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129173758</v>
+      </c>
+      <c r="B14" t="n">
+        <v>81019</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>651247</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6674062</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129173780</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91934</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>651282</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6673979</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129173772</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91523</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>651329</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6673992</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129173805</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92854</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>651256</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6673992</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129173813</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92854</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>651303</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6673916</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129173742</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>651328</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6673988</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129173806</v>
       </c>
       <c r="B2" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129173762</v>
       </c>
       <c r="B3" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129173810</v>
       </c>
       <c r="B4" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129173809</v>
       </c>
       <c r="B5" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129173815</v>
       </c>
       <c r="B11" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>129173816</v>
       </c>
       <c r="B12" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>129173758</v>
       </c>
       <c r="B14" t="n">
-        <v>81019</v>
+        <v>81020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,32 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129173780</v>
+        <v>129173772</v>
       </c>
       <c r="B15" t="n">
-        <v>91934</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651282</v>
+        <v>651329</v>
       </c>
       <c r="R15" t="n">
-        <v>6673979</v>
+        <v>6673992</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,32 +2294,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129173772</v>
+        <v>129173780</v>
       </c>
       <c r="B16" t="n">
-        <v>91523</v>
+        <v>91937</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651329</v>
+        <v>651282</v>
       </c>
       <c r="R16" t="n">
-        <v>6673992</v>
+        <v>6673979</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,7 +2407,7 @@
         <v>129173805</v>
       </c>
       <c r="B17" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>129173813</v>
       </c>
       <c r="B18" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -2184,32 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129173772</v>
+        <v>129173780</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>91937</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651329</v>
+        <v>651282</v>
       </c>
       <c r="R15" t="n">
-        <v>6673992</v>
+        <v>6673979</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,32 +2294,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129173780</v>
+        <v>129173772</v>
       </c>
       <c r="B16" t="n">
-        <v>91937</v>
+        <v>91526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651282</v>
+        <v>651329</v>
       </c>
       <c r="R16" t="n">
-        <v>6673979</v>
+        <v>6673992</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129173806</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129173762</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129173810</v>
       </c>
       <c r="B4" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129173809</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129173815</v>
       </c>
       <c r="B11" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>129173816</v>
       </c>
       <c r="B12" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129173744</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>129173758</v>
       </c>
       <c r="B14" t="n">
-        <v>81020</v>
+        <v>81024</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>129173780</v>
       </c>
       <c r="B15" t="n">
-        <v>91937</v>
+        <v>91944</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>129173772</v>
       </c>
       <c r="B16" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>129173805</v>
       </c>
       <c r="B17" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,45 +2514,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173813</v>
+        <v>129173742</v>
       </c>
       <c r="B18" t="n">
-        <v>92857</v>
+        <v>5197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2560,10 +2558,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651303</v>
+        <v>651328</v>
       </c>
       <c r="R18" t="n">
-        <v>6673916</v>
+        <v>6673988</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2595,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2603,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,43 +2630,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129173742</v>
+        <v>129173813</v>
       </c>
       <c r="B19" t="n">
-        <v>5197</v>
+        <v>92864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651328</v>
+        <v>651303</v>
       </c>
       <c r="R19" t="n">
-        <v>6673988</v>
+        <v>6673916</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -2514,43 +2514,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173742</v>
+        <v>129173813</v>
       </c>
       <c r="B18" t="n">
-        <v>5197</v>
+        <v>92864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2558,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651328</v>
+        <v>651303</v>
       </c>
       <c r="R18" t="n">
-        <v>6673988</v>
+        <v>6673916</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2593,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2603,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,45 +2632,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129173813</v>
+        <v>129173742</v>
       </c>
       <c r="B19" t="n">
-        <v>92864</v>
+        <v>5197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651303</v>
+        <v>651328</v>
       </c>
       <c r="R19" t="n">
-        <v>6673916</v>
+        <v>6673988</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129173806</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129173762</v>
       </c>
       <c r="B3" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129173810</v>
       </c>
       <c r="B4" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129173809</v>
       </c>
       <c r="B5" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129173815</v>
       </c>
       <c r="B11" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>129173816</v>
       </c>
       <c r="B12" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2184,32 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129173780</v>
+        <v>129173772</v>
       </c>
       <c r="B15" t="n">
-        <v>91944</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651282</v>
+        <v>651329</v>
       </c>
       <c r="R15" t="n">
-        <v>6673979</v>
+        <v>6673992</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,32 +2294,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129173772</v>
+        <v>129173780</v>
       </c>
       <c r="B16" t="n">
-        <v>91533</v>
+        <v>91951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651329</v>
+        <v>651282</v>
       </c>
       <c r="R16" t="n">
-        <v>6673992</v>
+        <v>6673979</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,7 +2407,7 @@
         <v>129173805</v>
       </c>
       <c r="B17" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>129173813</v>
       </c>
       <c r="B18" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129173806</v>
       </c>
       <c r="B2" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129173762</v>
       </c>
       <c r="B3" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129173810</v>
       </c>
       <c r="B4" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129173809</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129173815</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>129173816</v>
       </c>
       <c r="B12" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129173744</v>
       </c>
       <c r="B13" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>129173758</v>
       </c>
       <c r="B14" t="n">
-        <v>81024</v>
+        <v>81026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>129173772</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>129173780</v>
       </c>
       <c r="B16" t="n">
-        <v>91951</v>
+        <v>91953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>129173805</v>
       </c>
       <c r="B17" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>129173813</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129173806</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129173762</v>
       </c>
       <c r="B3" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129173810</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129173809</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129173815</v>
+        <v>129173816</v>
       </c>
       <c r="B11" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1765,10 +1769,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651373</v>
+        <v>651311</v>
       </c>
       <c r="R11" t="n">
-        <v>6673998</v>
+        <v>6673958</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1800,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1841,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129173816</v>
+        <v>129173815</v>
       </c>
       <c r="B12" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,11 +1874,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651311</v>
+        <v>651373</v>
       </c>
       <c r="R12" t="n">
-        <v>6673958</v>
+        <v>6673998</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2184,32 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129173772</v>
+        <v>129173780</v>
       </c>
       <c r="B15" t="n">
-        <v>91542</v>
+        <v>91962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651329</v>
+        <v>651282</v>
       </c>
       <c r="R15" t="n">
-        <v>6673992</v>
+        <v>6673979</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,32 +2294,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129173780</v>
+        <v>129173772</v>
       </c>
       <c r="B16" t="n">
-        <v>91953</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651282</v>
+        <v>651329</v>
       </c>
       <c r="R16" t="n">
-        <v>6673979</v>
+        <v>6673992</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,7 +2407,7 @@
         <v>129173805</v>
       </c>
       <c r="B17" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>129173813</v>
       </c>
       <c r="B18" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129173806</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129173810</v>
       </c>
       <c r="B4" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129173809</v>
       </c>
       <c r="B5" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129173816</v>
       </c>
       <c r="B11" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129173815</v>
       </c>
       <c r="B12" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2184,32 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129173780</v>
+        <v>129173772</v>
       </c>
       <c r="B15" t="n">
-        <v>91962</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651282</v>
+        <v>651329</v>
       </c>
       <c r="R15" t="n">
-        <v>6673979</v>
+        <v>6673992</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,32 +2294,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129173772</v>
+        <v>129173780</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>91963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651329</v>
+        <v>651282</v>
       </c>
       <c r="R16" t="n">
-        <v>6673992</v>
+        <v>6673979</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,7 +2407,7 @@
         <v>129173805</v>
       </c>
       <c r="B17" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>129173813</v>
       </c>
       <c r="B18" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129173806</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129173762</v>
       </c>
       <c r="B3" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129173810</v>
       </c>
       <c r="B4" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129173809</v>
       </c>
       <c r="B5" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129173816</v>
+        <v>129173815</v>
       </c>
       <c r="B11" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,11 +1756,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1769,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651311</v>
+        <v>651373</v>
       </c>
       <c r="R11" t="n">
-        <v>6673958</v>
+        <v>6673998</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1804,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1810,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129173815</v>
+        <v>129173816</v>
       </c>
       <c r="B12" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1870,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651373</v>
+        <v>651311</v>
       </c>
       <c r="R12" t="n">
-        <v>6673998</v>
+        <v>6673958</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2077,7 +2077,7 @@
         <v>129173758</v>
       </c>
       <c r="B14" t="n">
-        <v>81026</v>
+        <v>81028</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,32 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129173772</v>
+        <v>129173780</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651329</v>
+        <v>651282</v>
       </c>
       <c r="R15" t="n">
-        <v>6673992</v>
+        <v>6673979</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,32 +2294,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129173780</v>
+        <v>129173772</v>
       </c>
       <c r="B16" t="n">
-        <v>91963</v>
+        <v>91543</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651282</v>
+        <v>651329</v>
       </c>
       <c r="R16" t="n">
-        <v>6673979</v>
+        <v>6673992</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,7 +2407,7 @@
         <v>129173805</v>
       </c>
       <c r="B17" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>129173813</v>
       </c>
       <c r="B18" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129173806</v>
+        <v>129173758</v>
       </c>
       <c r="B2" t="n">
-        <v>92901</v>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651274</v>
+        <v>651247</v>
       </c>
       <c r="R2" t="n">
-        <v>6673866</v>
+        <v>6674062</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129173762</v>
+        <v>129173760</v>
       </c>
       <c r="B3" t="n">
-        <v>91354</v>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651271</v>
+        <v>651224</v>
       </c>
       <c r="R3" t="n">
-        <v>6673857</v>
+        <v>6673914</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -858,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -868,7 +868,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ganska riklig mängd på undersidan av stubben.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129173810</v>
+        <v>122330399</v>
       </c>
       <c r="B4" t="n">
-        <v>92901</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,33 +911,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -941,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651294</v>
+        <v>651326</v>
       </c>
       <c r="R4" t="n">
-        <v>6673877</v>
+        <v>6673994</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -971,22 +968,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129173809</v>
+        <v>129173772</v>
       </c>
       <c r="B5" t="n">
-        <v>92901</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,14 +1044,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ackarebottnen, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651237</v>
+        <v>651329</v>
       </c>
       <c r="R5" t="n">
-        <v>6673840</v>
+        <v>6673992</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1086,7 +1083,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1093,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330399</v>
+        <v>129173761</v>
       </c>
       <c r="B6" t="n">
-        <v>90837</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651326</v>
+        <v>651318</v>
       </c>
       <c r="R6" t="n">
-        <v>6673994</v>
+        <v>6674069</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1196,22 +1188,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,62 +1230,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330349</v>
+        <v>129173762</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Ackarebottnen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651319</v>
+        <v>651271</v>
       </c>
       <c r="R7" t="n">
-        <v>6673998</v>
+        <v>6673857</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1320,22 +1298,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,51 +1340,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330348</v>
+        <v>129173780</v>
       </c>
       <c r="B8" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651275</v>
+        <v>651282</v>
       </c>
       <c r="R8" t="n">
-        <v>6674023</v>
+        <v>6673979</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1444,22 +1408,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,43 +1450,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330548</v>
+        <v>129173805</v>
       </c>
       <c r="B9" t="n">
-        <v>100510</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1530,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651297</v>
+        <v>651256</v>
       </c>
       <c r="R9" t="n">
-        <v>6673956</v>
+        <v>6673992</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1560,22 +1518,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,48 +1560,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330330</v>
+        <v>129173806</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1651,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651327</v>
+        <v>651274</v>
       </c>
       <c r="R10" t="n">
-        <v>6673995</v>
+        <v>6673866</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1681,22 +1628,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129173815</v>
+        <v>129173809</v>
       </c>
       <c r="B11" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,24 +1698,20 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Ackarebottnen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651373</v>
+        <v>651237</v>
       </c>
       <c r="R11" t="n">
-        <v>6673998</v>
+        <v>6673840</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1800,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129173816</v>
+        <v>129173810</v>
       </c>
       <c r="B12" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1810,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1883,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651311</v>
+        <v>651294</v>
       </c>
       <c r="R12" t="n">
-        <v>6673958</v>
+        <v>6673877</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1918,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129173744</v>
+        <v>129173813</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,35 +1909,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2002,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651279</v>
+        <v>651303</v>
       </c>
       <c r="R13" t="n">
-        <v>6673952</v>
+        <v>6673916</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2037,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +1989,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129173758</v>
+        <v>129173815</v>
       </c>
       <c r="B14" t="n">
-        <v>81055</v>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,24 +2027,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2112,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651247</v>
+        <v>651373</v>
       </c>
       <c r="R14" t="n">
-        <v>6674062</v>
+        <v>6673998</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2147,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2157,7 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129173772</v>
+        <v>129173816</v>
       </c>
       <c r="B15" t="n">
-        <v>91581</v>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,25 +2141,33 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2222,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651329</v>
+        <v>651311</v>
       </c>
       <c r="R15" t="n">
-        <v>6673992</v>
+        <v>6673958</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2257,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129173780</v>
+        <v>122330348</v>
       </c>
       <c r="B16" t="n">
-        <v>92004</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,26 +2259,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2332,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651282</v>
+        <v>651275</v>
       </c>
       <c r="R16" t="n">
-        <v>6673979</v>
+        <v>6674023</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2362,22 +2325,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,37 +2367,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129173805</v>
+        <v>122330349</v>
       </c>
       <c r="B17" t="n">
-        <v>92901</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2442,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651256</v>
+        <v>651319</v>
       </c>
       <c r="R17" t="n">
-        <v>6673992</v>
+        <v>6673998</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2472,22 +2444,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,45 +2486,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173813</v>
+        <v>129173744</v>
       </c>
       <c r="B18" t="n">
-        <v>92901</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2560,10 +2533,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651303</v>
+        <v>651279</v>
       </c>
       <c r="R18" t="n">
-        <v>6673916</v>
+        <v>6673952</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2595,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,10 +2605,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129173742</v>
+        <v>122330330</v>
       </c>
       <c r="B19" t="n">
-        <v>5197</v>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,21 +2616,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2666,7 +2639,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2676,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651328</v>
+        <v>651327</v>
       </c>
       <c r="R19" t="n">
-        <v>6673988</v>
+        <v>6673995</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2706,22 +2679,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,6 +2718,344 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129173749</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ackarebottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>651267</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6673854</v>
+      </c>
+      <c r="S20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129173742</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>651328</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6673988</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122330548</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>651297</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6673956</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 220-2025 artfynd.xlsx
+++ b/artfynd/A 220-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173760</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330399</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173772</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173761</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173762</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173780</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173805</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173806</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173809</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1895,6 +1950,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173810</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2013,6 +2073,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173813</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2127,6 +2192,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173815</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2245,6 +2315,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173816</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2364,6 +2439,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330348</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2483,6 +2563,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330349</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2602,6 +2687,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173744</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2718,6 +2808,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330330</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2829,6 +2924,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173749</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2945,6 +3045,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173742</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3056,8 +3161,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330548</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>